--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,1006 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -637,27 +637,31 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/24</t>
         </is>
       </c>
     </row>
@@ -748,27 +756,31 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +812,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/24</t>
         </is>
       </c>
     </row>
@@ -864,19 +880,19 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 12分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
@@ -887,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +927,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/24</t>
         </is>
       </c>
     </row>
@@ -998,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1068,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -1086,19 +1106,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 41分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
@@ -1109,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1153,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1173,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/24</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1516,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1577,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1627,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1688,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1738,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1799,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1849,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1910,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1960,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2021,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2071,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2132,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2182,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2243,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2293,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2354,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2404,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2465,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2515,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2576,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2626,788 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>2/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/24</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/24</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/24</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -875,27 +875,31 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 12分钟</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,12 +931,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -952,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/24</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -995,19 +999,19 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 20分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1042,17 +1046,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1062,13 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -1101,27 +1109,31 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:01采样，终点ETA 41分钟</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1129,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1153,12 +1165,12 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1178,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/24</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1294,7 +1306,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1332,19 +1344,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 52分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
@@ -1355,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1384,7 +1396,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1405,7 +1417,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1516,7 +1528,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1589,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1627,7 +1639,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1738,7 +1750,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1811,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1849,7 +1861,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1922,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1960,7 +1972,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2033,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2071,7 +2083,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2144,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2182,7 +2194,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2255,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2293,7 +2305,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2366,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2404,7 +2416,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2477,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2515,7 +2527,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2588,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2626,7 +2638,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2699,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2737,7 +2749,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2810,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2848,7 +2860,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2921,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2959,7 +2971,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3032,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3070,7 +3082,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3143,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3181,7 +3193,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3254,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3296,7 +3308,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/24</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3369,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3407,7 +3419,233 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/24</t>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>5/25</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,14 +446,14 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -994,27 +994,31 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 20分钟</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,12 +1050,12 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1061,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1130,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1141,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -1195,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -1228,27 +1232,31 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -1256,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1280,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -1339,27 +1351,31 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 52分钟</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1367,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1391,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -1450,27 +1470,31 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1478,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1502,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -1561,27 +1589,31 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1589,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1613,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1703,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq63，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1700,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1708,10 +1744,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -1729,7 +1781,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1750,7 +1802,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1783,27 +1835,31 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1811,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1835,17 +1891,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1855,13 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -1894,27 +1954,31 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1922,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1946,33 +2010,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2083,7 +2151,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2121,19 +2189,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 25分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
@@ -2144,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2168,17 +2236,17 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2188,13 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2305,7 +2377,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2416,7 +2488,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2527,7 +2599,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2638,7 +2710,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2749,7 +2821,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2882,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2860,7 +2932,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2993,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2971,7 +3043,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3104,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3082,7 +3154,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3215,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3193,7 +3265,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3326,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3308,7 +3380,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3441,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3419,7 +3491,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3552,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3530,7 +3602,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3538,22 +3610,22 @@
       <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3591,7 +3663,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3640,12 +3712,1043 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>4/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>132.0</t>
         </is>
       </c>
-      <c r="AC28" s="2" t="inlineStr">
-        <is>
-          <t>5/25</t>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>6/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>2/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>1/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>2/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>4/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,14 +1906,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2073,27 +2073,31 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2101,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,33 +2129,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -2184,27 +2192,31 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2212,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2236,12 +2248,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2251,22 +2263,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -2299,27 +2311,31 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -2327,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2351,33 +2367,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -2410,27 +2430,31 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2438,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2462,33 +2486,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -2521,27 +2549,31 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2549,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2573,33 +2605,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>20/26</t>
         </is>
       </c>
     </row>
@@ -2632,27 +2668,31 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2660,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2684,33 +2724,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -2743,27 +2787,31 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2771,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2795,17 +2843,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2815,13 +2863,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>21/26</t>
         </is>
       </c>
     </row>
@@ -2854,27 +2906,31 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2882,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2906,33 +2962,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -2970,19 +3030,19 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 19分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
@@ -2993,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3017,17 +3077,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3037,13 +3097,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>19/26</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,19 +3256,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 22分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
@@ -3215,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3239,17 +3303,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3259,13 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3380,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3832,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3947,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4062,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4292,7 +4360,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4421,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4464,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4579,7 +4647,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4641,22 +4709,22 @@
       <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4689,12 +4757,12 @@
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4743,12 +4811,932 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>14/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>127.0</t>
         </is>
       </c>
-      <c r="AC37" s="2" t="inlineStr">
+      <c r="AC38" s="2" t="inlineStr">
         <is>
           <t>4/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>16/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>10/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>4/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>10/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>16/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>7/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>20/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>18/26</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>20/26</t>
+          <t>22/26</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/26</t>
+          <t>24/26</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3035,17 +3035,21 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 19分钟</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -3053,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,12 +3081,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3092,22 +3096,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/26</t>
+          <t>20/26</t>
         </is>
       </c>
     </row>
@@ -3140,27 +3144,31 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3168,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,17 +3200,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3212,13 +3220,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>23/26</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3263,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3261,17 +3273,21 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 22分钟</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3279,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,12 +3319,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3318,22 +3334,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -3366,27 +3382,31 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3394,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3418,17 +3438,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3438,17 +3458,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -3481,27 +3501,31 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3509,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3533,17 +3557,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3553,13 +3577,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>21/26</t>
         </is>
       </c>
     </row>
@@ -3597,19 +3625,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：11:01采样，终点ETA 6分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
@@ -3620,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3644,33 +3672,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>19/26</t>
         </is>
       </c>
     </row>
@@ -3703,27 +3735,31 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3731,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3755,17 +3791,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3775,17 +3811,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -3818,27 +3854,31 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3846,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3870,37 +3910,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -3933,27 +3973,31 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3961,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3985,37 +4029,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>18/26</t>
         </is>
       </c>
     </row>
@@ -4048,27 +4092,31 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4076,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4100,17 +4148,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4120,17 +4168,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -4168,19 +4216,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：11:20采样，终点ETA 25分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
@@ -4191,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4215,17 +4263,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4235,17 +4283,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4360,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -4388,12 +4436,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq47，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4421,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4429,10 +4477,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>09:38</t>
@@ -4450,7 +4514,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4532,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4647,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4762,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4816,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4931,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -4992,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5046,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5161,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5276,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5391,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5506,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5621,7 +5685,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5736,7 +5800,697 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
+          <t>22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
           <t>20/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>13/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>19/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>14/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>18/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>17/26</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2030,17 +2030,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>19/26</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/26</t>
+          <t>18/26</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -3978,24 +3978,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -4211,27 +4211,31 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:20采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -4239,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,12 +4267,12 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4288,12 +4292,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -4326,27 +4330,31 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4354,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4378,17 +4386,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4398,17 +4406,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4449,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq47，推进9站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4469,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4524,7 +4532,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4568,27 +4576,31 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4596,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4620,37 +4632,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -4683,27 +4695,31 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4711,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4735,17 +4751,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4755,17 +4771,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -4798,27 +4814,31 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -4826,7 +4846,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4850,17 +4870,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4870,17 +4890,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>17/26</t>
         </is>
       </c>
     </row>
@@ -4913,27 +4933,31 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -4941,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4965,17 +4989,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4985,17 +5009,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -5028,27 +5052,31 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5056,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,17 +5108,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5100,17 +5128,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>19/26</t>
         </is>
       </c>
     </row>
@@ -5143,27 +5171,31 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -5171,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5195,17 +5227,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5215,7 +5247,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5225,7 +5257,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5318,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,7 +5357,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5340,7 +5372,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -5378,19 +5410,19 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：12:20采样，终点ETA 45分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
@@ -5401,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5425,17 +5457,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5445,17 +5477,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5570,7 +5602,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5685,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5861,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5915,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -5976,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6091,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6145,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6260,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>19/26</t>
+          <t>18/26</t>
         </is>
       </c>
     </row>
@@ -6298,22 +6330,26 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>12:20采样：该车到重点站川周公路康沈路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6321,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6345,17 +6381,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6365,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6419,22 @@
       <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6431,12 +6467,12 @@
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6450,47 +6486,499 @@
       <c r="T51" s="2" t="inlineStr"/>
       <c r="U51" s="2" t="inlineStr">
         <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="V51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W51" s="2" t="inlineStr">
+      <c r="W52" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X51" s="2" t="inlineStr">
+      <c r="X52" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y51" s="2" t="inlineStr">
+      <c r="Y52" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z51" s="2" t="inlineStr">
+      <c r="Z52" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
+      <c r="AA52" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB51" s="2" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>18/26</t>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>13/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>1/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>19/26</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,14 +2382,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2620,22 +2620,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>22/26</t>
+          <t>22/27</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2744,17 +2744,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>24/26</t>
+          <t>24/27</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2977,22 +2977,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>20/26</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>23/26</t>
+          <t>23/27</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3334,22 +3334,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/26</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/26</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4049,17 +4049,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4652,17 +4652,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>19/26</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5242,14 +5242,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -5290,27 +5290,31 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5318,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,17 +5346,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5362,17 +5366,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5409,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5415,17 +5419,21 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:20采样，终点ETA 45分钟</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5433,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5457,12 +5465,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5482,12 +5490,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -5520,27 +5528,31 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5548,7 +5560,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5572,17 +5584,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5592,17 +5604,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -5635,27 +5647,31 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5663,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5687,37 +5703,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -5750,27 +5766,31 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5778,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,37 +5822,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/26</t>
+          <t>22/27</t>
         </is>
       </c>
     </row>
@@ -5870,19 +5890,19 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 23分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
@@ -5893,7 +5913,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,37 +5937,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -5980,27 +6000,31 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -6008,7 +6032,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6032,17 +6056,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6052,17 +6076,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>20/26</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6201,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6292,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>18/26</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -6330,19 +6354,19 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站川周公路康沈路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+          <t>13:20采样：该车到重点站锦绣路花木路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -6357,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6406,12 +6430,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6522,7 +6546,7 @@
       <c r="AB51" s="2" t="inlineStr"/>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6560,22 +6584,26 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>13:20采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6583,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6607,17 +6635,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6627,17 +6655,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6748,7 +6776,7 @@
       <c r="AB53" s="2" t="inlineStr"/>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6786,22 +6814,26 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>13:20采样：该车到重点站金杨路金业路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6809,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6833,17 +6865,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6853,17 +6885,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -6871,22 +6903,22 @@
       <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6919,12 +6951,12 @@
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6938,47 +6970,618 @@
       <c r="T55" s="2" t="inlineStr"/>
       <c r="U55" s="2" t="inlineStr">
         <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
           <t>13:20</t>
         </is>
       </c>
-      <c r="V55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W55" s="2" t="inlineStr">
+      <c r="W56" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X55" s="2" t="inlineStr">
+      <c r="X56" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y55" s="2" t="inlineStr">
+      <c r="Y56" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z55" s="2" t="inlineStr">
+      <c r="Z56" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB55" s="2" t="inlineStr">
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
         </is>
       </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>1/26</t>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>22/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>13/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2387,17 +2387,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>24/27</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5247,17 +5247,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5885,27 +5885,31 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 23分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5913,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5937,12 +5941,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5962,12 +5966,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6036,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6086,7 +6090,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6186,7 +6190,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6201,7 +6205,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6316,7 +6320,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6349,29 +6353,29 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站锦绣路花木路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6381,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6405,12 +6409,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6430,12 +6434,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6550,7 @@
       <c r="AB51" s="2" t="inlineStr"/>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6584,19 +6588,19 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+          <t>13:41采样：该车到重点站浦建路锦绣路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -6611,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6660,12 +6664,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6776,7 +6780,7 @@
       <c r="AB53" s="2" t="inlineStr"/>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6814,19 +6818,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站金杨路金业路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±5分钟</t>
+          <t>13:41采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -6841,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6890,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7006,7 +7010,7 @@
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7044,22 +7048,26 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>13:41采样：该车到重点站博兴路兰城路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7067,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7091,17 +7099,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7111,17 +7119,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7167,26 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>13:41采样：该车到重点站沪南路华夏西路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -7182,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7206,17 +7218,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7226,17 +7238,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7351,7 +7363,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7466,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7576,12 +7588,238 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>132.5</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1791,18 +1791,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1925,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2044,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2392,7 +2396,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2462,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2511,12 +2515,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2625,12 +2629,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2873,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2982,7 +2986,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3057,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3106,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3339,17 +3343,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3572,14 +3576,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>142.0</t>
@@ -3587,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3692,17 +3696,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3940,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4054,12 +4058,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4163,14 +4167,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>132.5</t>
@@ -4178,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4301,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4401,22 +4405,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4608,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4657,12 +4661,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4785,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4904,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5023,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5142,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5252,7 +5256,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5322,7 +5326,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5371,12 +5375,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5723,7 +5727,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5798,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5842,12 +5846,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5917,7 +5921,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5961,17 +5965,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6009,24 +6013,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6036,7 +6040,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6085,12 +6089,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6155,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6205,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6238,27 +6242,31 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -6266,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6290,17 +6298,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6310,17 +6318,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6358,12 +6366,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -6385,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6424,22 +6432,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6467,12 +6475,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq41推进至seq52，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -6500,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6508,10 +6516,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q51" s="2" t="inlineStr"/>
-      <c r="R51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="S51" s="2" t="inlineStr"/>
-      <c r="T51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
           <t>12:28</t>
@@ -6529,7 +6549,7 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6588,19 +6608,19 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>13:41采样：该车到重点站浦建路锦绣路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
+          <t>14:20采样：该车到重点站周东路川周公路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数19分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -6615,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6664,12 +6684,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6702,27 +6722,31 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -6730,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6754,33 +6778,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB53" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6818,19 +6846,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>13:41采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+          <t>14:20采样：该车到重点站沪南路北中路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -6845,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6922,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6988,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7048,19 +7076,19 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>13:41采样：该车到重点站博兴路兰城路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±5分钟</t>
+          <t>14:20采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -7075,7 +7103,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7124,12 +7152,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -7167,19 +7195,19 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>13:41采样：该车到重点站沪南路华夏西路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
+          <t>14:20采样：该车到重点站锦绣路花木路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -7194,7 +7222,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7243,7 +7271,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7286,22 +7314,26 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>14:20采样：该车到重点站白桦路明月路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7309,7 +7341,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7333,17 +7365,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7353,7 +7385,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7401,22 +7433,26 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>14:20采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7424,7 +7460,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7448,17 +7484,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7468,12 +7504,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7516,22 +7552,26 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>14:20采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数115分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7539,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7563,17 +7603,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7583,17 +7623,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7765,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7819,7 +7859,467 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,14 +2862,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>153.0</t>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3219,14 +3219,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3343,17 +3343,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4172,17 +4172,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4410,17 +4410,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5846,17 +5846,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5965,17 +5965,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6366,24 +6366,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6437,17 +6437,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq41推进至seq52，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq41推进至seq58，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6603,29 +6603,29 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站周东路川周公路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数19分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6841,24 +6841,24 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站沪南路北中路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6960,27 +6960,31 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6988,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7012,17 +7016,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -7032,13 +7036,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB55" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7190,29 +7198,29 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站锦绣路花木路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7222,7 +7230,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7246,12 +7254,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7271,12 +7279,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7309,29 +7317,29 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站白桦路明月路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7341,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7365,12 +7373,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7390,7 +7398,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7433,7 +7441,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -7445,14 +7453,10 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 55分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7460,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7484,17 +7488,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7504,17 +7508,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -7552,26 +7556,22 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数115分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 51分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,17 +7603,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7623,17 +7623,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -8012,22 +8012,26 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>15:20采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8035,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,17 +8063,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8079,17 +8083,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -8127,22 +8131,26 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>15:20采样：该车到重点站康沈路秀康路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8150,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8174,17 +8182,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8194,17 +8202,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -8212,22 +8220,22 @@
       <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8260,12 +8268,12 @@
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8279,47 +8287,618 @@
       <c r="T66" s="2" t="inlineStr"/>
       <c r="U66" s="2" t="inlineStr">
         <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
           <t>15:25</t>
         </is>
       </c>
-      <c r="V66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W66" s="2" t="inlineStr">
+      <c r="W67" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X66" s="2" t="inlineStr">
+      <c r="X67" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y66" s="2" t="inlineStr">
+      <c r="Y67" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z66" s="2" t="inlineStr">
+      <c r="Z67" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
+      <c r="AA67" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
+      <c r="AB67" s="2" t="inlineStr">
         <is>
           <t>137.0</t>
         </is>
       </c>
-      <c r="AC66" s="2" t="inlineStr">
-        <is>
-          <t>17/28</t>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>26/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>25/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1910,14 +1910,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>138.5</t>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2034,17 +2034,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,22 +2267,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>27/28</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3100,14 +3100,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3343,17 +3343,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3581,17 +3581,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4775,17 +4775,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>138.5</t>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5013,17 +5013,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5484,22 +5484,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5965,17 +5965,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6079,14 +6079,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -7203,24 +7203,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -7322,12 +7322,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -7446,17 +7446,21 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 55分钟</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7464,7 +7468,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7488,17 +7492,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7508,12 +7512,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7551,27 +7555,31 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 51分钟</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7579,7 +7587,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,17 +7611,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7623,17 +7631,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -7666,27 +7674,31 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>13:31</t>
@@ -7694,7 +7706,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7718,17 +7730,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7738,13 +7750,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7897,19 +7913,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 42分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
@@ -7920,7 +7936,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7944,17 +7960,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7964,17 +7980,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -8007,24 +8023,24 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -8039,7 +8055,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,12 +8079,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8088,12 +8104,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -8131,19 +8147,19 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站康沈路秀康路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±5分钟</t>
+          <t>16:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -8158,7 +8174,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8207,12 +8223,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8384,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8438,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -8476,22 +8492,26 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>16:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8499,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8523,17 +8543,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8543,17 +8563,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8668,7 +8688,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>27/28</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8821,22 +8841,26 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>16:20采样：该车到重点站沪南路华夏西路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8844,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8868,37 +8892,961 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>132.3</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>132.3</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X71" s="2" t="inlineStr">
+      <c r="X73" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="Y73" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z71" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA71" s="2" t="inlineStr">
+      <c r="Z73" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>4/28</t>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC79"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>136.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1915,17 +1915,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,14 +2148,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3105,17 +3105,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3457,14 +3457,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>136.0</t>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3576,22 +3576,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3696,17 +3696,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3815,17 +3815,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4894,17 +4894,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5127,14 +5127,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6084,17 +6084,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6318,17 +6318,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6679,17 +6679,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7679,12 +7679,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7745,17 +7745,17 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7908,27 +7908,31 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 42分钟</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7936,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7960,12 +7964,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7975,22 +7979,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -8028,24 +8032,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8055,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8104,12 +8108,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -8142,24 +8146,24 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -8174,7 +8178,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8198,12 +8202,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8213,7 +8217,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8223,12 +8227,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -8256,12 +8260,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq55，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -8289,7 +8293,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,10 +8301,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q66" s="2" t="inlineStr"/>
-      <c r="R66" s="2" t="inlineStr"/>
-      <c r="S66" s="2" t="inlineStr"/>
-      <c r="T66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
           <t>15:22</t>
@@ -8318,7 +8338,7 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8400,7 +8420,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8454,7 +8474,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -8487,29 +8507,29 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8519,7 +8539,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8543,12 +8563,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8568,12 +8588,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8654,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8749,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8841,19 +8861,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站沪南路华夏西路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+          <t>17:20采样：该车到重点站锦绣路罗山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -8868,7 +8888,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8917,12 +8937,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -8960,19 +8980,19 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±5分钟</t>
+          <t>17:20采样：该车到重点站迎春路金松路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -8987,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9036,12 +9056,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9194,22 +9214,26 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>17:20采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -9217,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9241,17 +9265,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9261,17 +9285,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -9309,22 +9333,26 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>17:20采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9332,7 +9360,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9356,17 +9384,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9376,17 +9404,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -9424,22 +9452,26 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>17:20采样：该车到重点站白桦路明月路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -9447,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9471,17 +9503,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9491,17 +9523,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -9539,22 +9571,26 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>17:20采样：该车到重点站沪南路高科西路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -9562,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9586,17 +9622,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9606,17 +9642,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -9654,22 +9690,26 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>17:20采样：该车到重点站康沈路秀康路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9677,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9701,17 +9741,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9721,17 +9761,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -9769,22 +9809,26 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>17:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -9792,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9816,37 +9860,842 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>136.3</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X79" s="2" t="inlineStr">
+      <c r="X80" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y79" s="2" t="inlineStr">
+      <c r="Y80" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z79" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA79" s="2" t="inlineStr">
+      <c r="Z80" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
-        <is>
-          <t>138.5</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr">
-        <is>
-          <t>21/28</t>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>26/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>132.7</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>125.7</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>132.7</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:AC87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1791,22 +1791,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4656,17 +4656,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5132,17 +5132,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6793,22 +6793,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6917,17 +6917,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq55，推进17站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq60，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8397,19 +8397,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：17:31采样，终点ETA 10分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr"/>
@@ -8420,7 +8420,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8444,37 +8444,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8861,19 +8861,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站锦绣路罗山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站迎春路金松路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站云山路碧云路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -9214,19 +9214,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站迎春路金松路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -9333,19 +9333,19 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站迎春路长柳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9452,19 +9452,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站白桦路明月路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站丁香路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9571,19 +9571,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站沪南路高科西路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站沪南路高科西路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -9690,19 +9690,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站康沈路秀康路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -9809,19 +9809,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站金杨路金业路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10043,22 +10043,26 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>17:31采样：该车到重点站川周公路康沈路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数113分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10066,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10090,17 +10094,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10110,17 +10114,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -10158,22 +10162,26 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>17:31采样：该车到重点站莱阳路东陆路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10181,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10205,17 +10213,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10225,17 +10233,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10411,7 +10419,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10526,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10641,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10699,6 +10707,121 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC87"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1796,17 +1796,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,22 +2743,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>27/28</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3581,17 +3581,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4172,17 +4172,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5603,22 +5603,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5727,17 +5727,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6570,7 +6570,7 @@
       <c r="AB51" s="2" t="inlineStr"/>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6798,17 +6798,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7036,17 +7036,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7393,17 +7393,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7984,17 +7984,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8222,17 +8222,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8359,7 +8359,7 @@
       <c r="AB66" s="2" t="inlineStr"/>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -8420,7 +8420,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8464,17 +8464,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8626,27 +8626,31 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8654,7 +8658,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8678,37 +8682,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>27/28</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -8741,27 +8745,31 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8769,7 +8777,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8793,37 +8801,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8856,29 +8864,29 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8888,7 +8896,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8912,12 +8920,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8937,12 +8945,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8980,26 +8988,22 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站云山路碧云路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 14分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9007,7 +9011,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9036,7 +9040,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9056,12 +9060,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9099,19 +9103,19 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 9分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr"/>
@@ -9122,7 +9126,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9146,17 +9150,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9166,17 +9170,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9214,26 +9218,22 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站迎春路金松路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 22分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9333,26 +9333,22 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站迎春路长柳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 32分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9360,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9384,12 +9380,12 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9399,7 +9395,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9409,12 +9405,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -9452,19 +9448,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站丁香路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站康沈路秀沿路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -9479,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9528,12 +9524,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -9571,19 +9567,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站沪南路高科西路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站长岛路张杨北路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -9598,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9647,12 +9643,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9690,19 +9686,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -9717,7 +9713,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9766,12 +9762,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9809,19 +9805,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站金杨路金业路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站沪南路御桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -9836,7 +9832,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9885,12 +9881,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10005,7 +10001,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -10043,19 +10039,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站川周公路康沈路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数113分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站迎春路金松路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -10070,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10119,12 +10115,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>132.8</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -10162,19 +10158,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站莱阳路东陆路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -10189,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10238,12 +10234,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -10281,22 +10277,26 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>18:21采样：该车到重点站沪南路华夏西路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10328,17 +10328,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10348,17 +10348,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -10396,22 +10396,26 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>18:21采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10419,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10443,17 +10447,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10463,17 +10467,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -10511,22 +10515,26 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>18:21采样：该车到重点站沪南路华夏西路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10534,7 +10542,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10558,17 +10566,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10578,17 +10586,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -10626,22 +10634,26 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>18:21采样：该车到重点站金杨路金业路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10649,7 +10661,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10673,17 +10685,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10693,17 +10705,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -10741,22 +10753,26 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>18:21采样：该车到重点站川周公路康沈路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -10764,7 +10780,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10788,37 +10804,838 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X87" s="2" t="inlineStr">
+      <c r="X88" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y87" s="2" t="inlineStr">
+      <c r="Y88" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z87" s="2" t="inlineStr">
+      <c r="Z88" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA87" s="2" t="inlineStr">
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>18:21采样：该车到重点站莱阳路东陆路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>135.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB87" s="2" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="AC87" s="2" t="inlineStr">
-        <is>
-          <t>15/28</t>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>27/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>133.7</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>126.2</t>
+          <t>125.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>126.2</t>
+          <t>125.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7031,14 +7031,14 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
           <t>134.5</t>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>126.2</t>
+          <t>125.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8983,27 +8983,31 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 14分钟</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9011,7 +9015,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9035,12 +9039,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9060,12 +9064,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9165,14 +9169,14 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
           <t>134.5</t>
@@ -9180,7 +9184,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -9213,27 +9217,31 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 22分钟</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -9241,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9265,12 +9273,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9280,7 +9288,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9290,12 +9298,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9328,27 +9336,31 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 32分钟</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9356,7 +9368,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9380,12 +9392,12 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9405,7 +9417,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9443,29 +9455,29 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站康沈路秀沿路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9475,7 +9487,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9499,12 +9511,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9524,12 +9536,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -9567,19 +9579,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站长岛路张杨北路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>18:40采样：该车到重点站东波路莱阳路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -9594,7 +9606,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9643,12 +9655,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9698,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -9698,7 +9710,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>18:31采样：该车到重点站五莲路兰城路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数24分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -9713,7 +9725,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9805,19 +9817,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站沪南路御桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>18:40采样：该车到重点站康沈路秀沿路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -9832,7 +9844,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9881,12 +9893,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10051,7 +10063,7 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站迎春路金松路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>18:40采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -10066,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10120,7 +10132,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10158,19 +10170,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±5分钟</t>
+          <t>18:31采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -10185,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10234,7 +10246,7 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10282,14 +10294,14 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站沪南路华夏西路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+          <t>18:40采样：该车到重点站迎春路金松路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -10304,7 +10316,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10353,7 +10365,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10396,19 +10408,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±5分钟</t>
+          <t>18:40采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10423,7 +10435,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10472,7 +10484,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10515,19 +10527,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站沪南路华夏西路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+          <t>18:40采样：该车到重点站沪南路高科西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10542,7 +10554,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10591,7 +10603,7 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>126.2</t>
+          <t>125.8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10646,7 +10658,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站金杨路金业路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±5分钟</t>
+          <t>18:40采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10661,7 +10673,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10715,7 +10727,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10753,19 +10765,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站川周公路康沈路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±5分钟</t>
+          <t>18:40采样：该车到重点站沪南路高科西路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10780,7 +10792,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10829,12 +10841,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -10895,7 +10907,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10983,19 +10995,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站莱阳路东陆路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±5分钟</t>
+          <t>18:40采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -11010,7 +11022,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11059,12 +11071,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11102,22 +11114,26 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>18:40采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11125,7 +11141,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11149,17 +11165,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11169,12 +11185,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11240,7 +11256,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11351,7 +11367,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11466,7 +11482,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11520,7 +11536,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -11528,22 +11544,22 @@
       <c r="A94" s="2" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11576,12 +11592,12 @@
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11595,47 +11611,277 @@
       <c r="T94" s="2" t="inlineStr"/>
       <c r="U94" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W94" s="2" t="inlineStr">
+      <c r="W95" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X94" s="2" t="inlineStr">
+      <c r="X95" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y94" s="2" t="inlineStr">
+      <c r="Y95" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z94" s="2" t="inlineStr">
+      <c r="Z95" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA94" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB94" s="2" t="inlineStr">
-        <is>
-          <t>133.7</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr">
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
         <is>
           <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC96"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1910,22 +1910,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,14 +2267,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>151.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>125.8</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3815,17 +3815,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4286,22 +4286,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4775,17 +4775,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4889,22 +4889,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5484,14 +5484,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>125.8</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>125.8</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7750,17 +7750,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8583,17 +8583,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>151.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8821,17 +8821,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9054,14 +9054,14 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9412,17 +9412,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -9460,24 +9460,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9526,22 +9526,22 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -9574,12 +9574,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>18:40采样：该车到重点站东波路莱阳路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站五莲路兰城路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数24分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9749,12 +9749,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9812,24 +9812,24 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>18:40采样：该车到重点站康沈路秀沿路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9883,22 +9883,22 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -9931,27 +9931,31 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>13:31</t>
@@ -9959,7 +9963,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9983,17 +9987,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -10003,17 +10007,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -10051,26 +10055,22 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>18:40采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10170,26 +10170,22 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10197,7 +10193,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10226,7 +10222,7 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10246,12 +10242,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -10289,19 +10285,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:40采样：该车到重点站迎春路金松路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站长岛路张杨北路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -10316,7 +10312,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10365,12 +10361,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -10408,19 +10404,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>18:40采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10435,7 +10431,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10484,7 +10480,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10527,19 +10523,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>18:40采样：该车到重点站沪南路高科西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站金杨路金口路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10554,7 +10550,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10603,7 +10599,7 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>125.8</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10646,19 +10642,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:40采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站沪南路御桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10673,7 +10669,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10722,7 +10718,7 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10765,19 +10761,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>18:40采样：该车到重点站沪南路高科西路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10792,7 +10788,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10841,12 +10837,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -10907,7 +10903,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10995,19 +10991,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>18:40采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -11022,7 +11018,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11071,12 +11067,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -11114,19 +11110,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>18:40采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站沪南路高科西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -11141,7 +11137,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11190,7 +11186,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>151.7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11256,7 +11252,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11344,22 +11340,26 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11391,17 +11391,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11411,17 +11411,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -11459,22 +11459,26 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站金杨路金业路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -11482,7 +11486,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11506,17 +11510,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11526,17 +11530,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -11574,22 +11578,26 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站博兴路兰城路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -11597,7 +11605,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11621,17 +11629,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11641,12 +11649,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11689,22 +11697,26 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11712,7 +11724,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11736,17 +11748,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11756,17 +11768,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -11774,24 +11786,24 @@
       <c r="A96" s="2" t="inlineStr"/>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -11804,30 +11816,34 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站莱阳路东陆路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11841,47 +11857,622 @@
       <c r="T96" s="2" t="inlineStr"/>
       <c r="U96" s="2" t="inlineStr">
         <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W96" s="2" t="inlineStr">
+      <c r="W97" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X96" s="2" t="inlineStr">
+      <c r="X97" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y96" s="2" t="inlineStr">
+      <c r="Y97" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z96" s="2" t="inlineStr">
+      <c r="Z97" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA96" s="2" t="inlineStr">
+      <c r="AA97" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB96" s="2" t="inlineStr">
+      <c r="AB97" s="2" t="inlineStr">
         <is>
           <t>134.5</t>
         </is>
       </c>
-      <c r="AC96" s="2" t="inlineStr">
+      <c r="AC97" s="2" t="inlineStr">
         <is>
           <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>136.3</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>131.3</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>136.7</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC101"/>
+  <dimension ref="A1:AC104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1915,17 +1915,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,14 +2148,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>137.0</t>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2272,17 +2272,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2624,17 +2624,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,17 +2743,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>151.7</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>124.2</t>
+          <t>124.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3696,17 +3696,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4894,17 +4894,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5127,14 +5127,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>137.0</t>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5489,17 +5489,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>124.2</t>
+          <t>124.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5841,17 +5841,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6318,17 +6318,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>124.2</t>
+          <t>124.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7507,17 +7507,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7989,12 +7989,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>151.7</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9059,17 +9059,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9650,17 +9650,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9888,17 +9888,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -10165,12 +10165,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -10182,10 +10182,14 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 19分钟</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10193,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10217,12 +10221,12 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10232,14 +10236,14 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
           <t>137.0</t>
@@ -10247,7 +10251,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -10280,29 +10284,29 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站长岛路张杨北路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10312,7 +10316,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10336,12 +10340,12 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10361,7 +10365,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10399,29 +10403,29 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10431,7 +10435,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10455,12 +10459,12 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10480,12 +10484,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -10518,29 +10522,29 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站金杨路金口路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10550,7 +10554,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10574,12 +10578,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10599,7 +10603,7 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>124.2</t>
+          <t>124.8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10637,29 +10641,29 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站沪南路御桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10669,7 +10673,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10693,12 +10697,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10718,12 +10722,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -10761,19 +10765,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>19:31采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10788,7 +10792,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10837,12 +10841,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10870,12 +10874,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq40推进至seq62，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -10903,7 +10907,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10911,10 +10915,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q88" s="2" t="inlineStr"/>
-      <c r="R88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
       <c r="S88" s="2" t="inlineStr"/>
-      <c r="T88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U88" s="2" t="inlineStr">
         <is>
           <t>18:12</t>
@@ -10932,7 +10948,7 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10991,26 +11007,22 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 15分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11018,7 +11030,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11047,7 +11059,7 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11057,17 +11069,17 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11105,29 +11117,29 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站沪南路高科西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11137,7 +11149,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11161,12 +11173,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11186,7 +11198,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>151.7</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11252,7 +11264,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11340,26 +11352,22 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:10采样，终点ETA 49分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11367,7 +11375,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11391,17 +11399,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11411,12 +11419,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11459,19 +11467,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站金杨路金业路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±5分钟</t>
+          <t>20:10采样：该车到重点站沪南路北中路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -11486,7 +11494,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11535,12 +11543,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11578,19 +11586,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站博兴路兰城路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
+          <t>20:01采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -11605,7 +11613,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11654,12 +11662,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -11697,19 +11705,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±5分钟</t>
+          <t>20:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -11724,7 +11732,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11773,12 +11781,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11816,19 +11824,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站莱阳路东陆路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+          <t>20:20采样：该车到重点站浦建路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -11843,7 +11851,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11892,7 +11900,7 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11935,22 +11943,26 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>20:20采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -11958,7 +11970,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11982,17 +11994,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12002,12 +12014,12 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -12050,22 +12062,26 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>20:20采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -12073,7 +12089,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12097,17 +12113,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12117,17 +12133,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12165,22 +12181,26 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>20:20采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -12188,7 +12208,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12212,17 +12232,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12232,12 +12252,12 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12280,22 +12300,26 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>20:20采样：该车到重点站白桦路明月路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12303,7 +12327,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12327,17 +12351,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12347,17 +12371,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -12365,24 +12389,24 @@
       <c r="A101" s="2" t="inlineStr"/>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12395,30 +12419,34 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>20:20采样：该车到重点站博兴路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数115分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12432,47 +12460,396 @@
       <c r="T101" s="2" t="inlineStr"/>
       <c r="U101" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>140.8</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>22:25</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>140分钟</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>20:20采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W101" s="2" t="inlineStr">
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X101" s="2" t="inlineStr">
+      <c r="X103" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y101" s="2" t="inlineStr">
+      <c r="Y103" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z101" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA101" s="2" t="inlineStr">
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB101" s="2" t="inlineStr">
-        <is>
-          <t>136.7</t>
-        </is>
-      </c>
-      <c r="AC101" s="2" t="inlineStr">
-        <is>
-          <t>18/29</t>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>135.3</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2748,17 +2748,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3105,17 +3105,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3696,17 +3696,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5132,17 +5132,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5608,17 +5608,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6084,17 +6084,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6318,17 +6318,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7041,12 +7041,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8821,17 +8821,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9650,17 +9650,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10241,17 +10241,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -10489,7 +10489,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11002,12 +11002,12 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -11019,10 +11019,14 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 15分钟</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11030,7 +11034,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11054,12 +11058,12 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11074,17 +11078,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -11122,24 +11126,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11149,7 +11153,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11198,12 +11202,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -11236,27 +11240,31 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>17:50</t>
@@ -11264,7 +11272,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11288,17 +11296,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11308,13 +11316,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB91" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11347,27 +11359,31 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:10采样，终点ETA 49分钟</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11375,7 +11391,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11399,17 +11415,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11419,17 +11435,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -11462,24 +11478,24 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>21:04</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>20:10采样：该车到重点站沪南路北中路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -11494,7 +11510,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11518,12 +11534,12 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11543,12 +11559,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11576,36 +11592,32 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>20:01采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -11613,7 +11625,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11621,10 +11633,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q94" s="2" t="inlineStr"/>
-      <c r="R94" s="2" t="inlineStr"/>
-      <c r="S94" s="2" t="inlineStr"/>
-      <c r="T94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U94" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -11637,17 +11665,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11657,17 +11685,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -11700,29 +11728,29 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11732,7 +11760,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11756,12 +11784,12 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11781,12 +11809,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11847,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -11836,12 +11864,12 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站浦建路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11851,7 +11879,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11875,12 +11903,12 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11905,7 +11933,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -11943,19 +11971,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
+          <t>20:40采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -11970,7 +11998,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12019,12 +12047,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -12052,36 +12080,32 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq49，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -12089,7 +12113,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12097,10 +12121,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr"/>
-      <c r="S98" s="2" t="inlineStr"/>
-      <c r="T98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12113,17 +12153,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12133,17 +12173,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -12181,19 +12221,19 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:46</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站东波路莱阳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -12208,7 +12248,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12257,7 +12297,7 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12295,29 +12335,29 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>21:56</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站白桦路明月路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -12327,7 +12367,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12351,12 +12391,12 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
@@ -12376,12 +12416,12 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -12419,19 +12459,19 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站博兴路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数115分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站周东路川周公路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -12446,7 +12486,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12495,12 +12535,12 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -12538,19 +12578,19 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>22:25</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -12565,7 +12605,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12614,12 +12654,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -12657,22 +12697,26 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>21:20采样：该车到重点站迎春路金松路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12680,7 +12724,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12704,17 +12748,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12724,17 +12768,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -12772,22 +12816,26 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>21:20采样：该车到重点站沪南路华夏西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -12795,7 +12843,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12819,17 +12867,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12839,17 +12887,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东35路.xlsx
+++ b/data/export/2026-09-19-浦东35路.xlsx
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5132,17 +5132,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10241,17 +10241,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11083,12 +11083,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11814,7 +11814,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12085,7 +12085,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq49，推进21站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -12216,29 +12216,29 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站东波路莱阳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -12454,29 +12454,29 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>22:07</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站周东路川周公路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
@@ -12578,26 +12578,22 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:50采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -12605,7 +12601,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12634,7 +12630,7 @@
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
@@ -12654,12 +12650,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -12697,26 +12693,22 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站迎春路金松路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:50采样，终点ETA 48分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12724,7 +12716,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12748,17 +12740,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12768,17 +12760,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -12816,19 +12808,19 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站沪南路华夏西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
+          <t>21:50采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -12843,7 +12835,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12892,12 +12884,12 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
